--- a/FINAL.xlsx
+++ b/FINAL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0968BC88-8C7D-4CAA-BB7C-FAA9F616E5F7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CE93213-AE7E-42E3-A03A-7CB61C6E657F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6650,7 +6650,7 @@
       </c>
       <c r="P19" s="54">
         <f ca="1">TODAY()</f>
-        <v>46262</v>
+        <v>46282</v>
       </c>
       <c r="Q19" s="54"/>
       <c r="R19" s="54"/>
@@ -9616,7 +9616,7 @@
     <mergeCell ref="B16:K16"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" scale="10" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>